--- a/data/trans_orig/P05A04-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P05A04-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2007</t>
+          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2007 (tasa de respuesta: 99,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>878500</t>
+          <t>879062</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>918262</t>
+          <t>921239</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1136520</t>
+          <t>1135670</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1181390</t>
+          <t>1181643</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2027513</t>
+          <t>2025232</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2090436</t>
+          <t>2087774</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,78%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87744</t>
+          <t>85537</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>124641</t>
+          <t>124797</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>96303</t>
+          <t>95240</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135632</t>
+          <t>136765</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>192056</t>
+          <t>193378</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>249837</t>
+          <t>248770</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>12894</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30012</t>
+          <t>30192</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17586</t>
+          <t>17348</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37660</t>
+          <t>36872</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34825</t>
+          <t>34976</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61631</t>
+          <t>61447</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1486378</t>
+          <t>1484356</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1534522</t>
+          <t>1531899</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1381525</t>
+          <t>1380769</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1430325</t>
+          <t>1430079</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2880493</t>
+          <t>2883994</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2951513</t>
+          <t>2952282</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,85%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>120243</t>
+          <t>121091</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>165189</t>
+          <t>166317</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>106730</t>
+          <t>104872</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>151848</t>
+          <t>149431</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>238562</t>
+          <t>237976</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>303032</t>
+          <t>302445</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13055</t>
+          <t>14087</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31236</t>
+          <t>31942</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28907</t>
+          <t>29109</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55121</t>
+          <t>54138</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46673</t>
+          <t>46251</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78937</t>
+          <t>79135</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>467487</t>
+          <t>466388</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>500298</t>
+          <t>498958</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>405656</t>
+          <t>404444</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>433632</t>
+          <t>432129</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>884787</t>
+          <t>882456</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>924339</t>
+          <t>924273</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,02%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30086</t>
+          <t>30311</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58693</t>
+          <t>56665</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32325</t>
+          <t>32891</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58316</t>
+          <t>59060</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71115</t>
+          <t>70561</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107727</t>
+          <t>108298</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9384</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27851</t>
+          <t>27175</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>13095</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14595</t>
+          <t>13897</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35275</t>
+          <t>35131</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2861751</t>
+          <t>2859621</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2930246</t>
+          <t>2929945</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2952014</t>
+          <t>2949403</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3023578</t>
+          <t>3023021</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5833325</t>
+          <t>5833430</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5936848</t>
+          <t>5931113</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,0%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>259211</t>
+          <t>256541</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>320905</t>
+          <t>326232</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>251516</t>
+          <t>256036</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>320428</t>
+          <t>321217</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>526663</t>
+          <t>533690</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>623516</t>
+          <t>626340</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>43989</t>
+          <t>44741</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>75171</t>
+          <t>77251</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56691</t>
+          <t>56876</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>92720</t>
+          <t>90920</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>107483</t>
+          <t>109209</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>156963</t>
+          <t>154712</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2012</t>
+          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2012 (tasa de respuesta: 99,17%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>885690</t>
+          <t>884453</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>918228</t>
+          <t>918087</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1198122</t>
+          <t>1196727</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1237212</t>
+          <t>1238231</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2093332</t>
+          <t>2093913</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2146864</t>
+          <t>2148107</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,44%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34593</t>
+          <t>35562</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63793</t>
+          <t>65914</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74802</t>
+          <t>72781</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>110645</t>
+          <t>111719</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118257</t>
+          <t>117090</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>164588</t>
+          <t>163840</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11992</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30582</t>
+          <t>29519</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10529</t>
+          <t>10850</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28570</t>
+          <t>28442</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26144</t>
+          <t>26992</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>50953</t>
+          <t>50811</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1729716</t>
+          <t>1729175</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1784316</t>
+          <t>1783372</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1559170</t>
+          <t>1556821</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1607872</t>
+          <t>1607686</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,47 +3294,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>89,53%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>92,46%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>3143</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>3342627</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>3303961</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3377846</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>90,72%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>89,67%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>92,47%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>3143</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>3342627</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>3303003</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3378351</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>90,72%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>89,64%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,67%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>126516</t>
+          <t>127661</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>173944</t>
+          <t>177471</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>101915</t>
+          <t>102660</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>146137</t>
+          <t>146800</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>239794</t>
+          <t>241605</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>303580</t>
+          <t>308142</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27518</t>
+          <t>27214</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54461</t>
+          <t>55988</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22323</t>
+          <t>20828</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45295</t>
+          <t>44277</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53991</t>
+          <t>54601</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88941</t>
+          <t>91049</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>418474</t>
+          <t>418978</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>446152</t>
+          <t>446205</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>396022</t>
+          <t>397394</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>422954</t>
+          <t>423504</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>825252</t>
+          <t>825386</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>862610</t>
+          <t>864064</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,01%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21527</t>
+          <t>21612</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45104</t>
+          <t>45650</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18995</t>
+          <t>19485</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42496</t>
+          <t>41981</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46319</t>
+          <t>45193</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77704</t>
+          <t>78946</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6060</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20871</t>
+          <t>21220</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>5670</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20649</t>
+          <t>20261</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14396</t>
+          <t>14325</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34826</t>
+          <t>34795</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3058971</t>
+          <t>3058262</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3129930</t>
+          <t>3127821</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3181554</t>
+          <t>3179207</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3246549</t>
+          <t>3249614</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6255380</t>
+          <t>6260801</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6354448</t>
+          <t>6357437</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,97%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198134</t>
+          <t>200662</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>259912</t>
+          <t>262825</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>216056</t>
+          <t>213612</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>274919</t>
+          <t>274691</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>427061</t>
+          <t>429685</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>516610</t>
+          <t>515539</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53009</t>
+          <t>54454</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>91527</t>
+          <t>90366</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>45567</t>
+          <t>46048</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>77484</t>
+          <t>78521</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>108037</t>
+          <t>108844</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>154758</t>
+          <t>155219</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2016</t>
+          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2016 (tasa de respuesta: 99,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>641056</t>
+          <t>641550</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>677515</t>
+          <t>676515</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>854587</t>
+          <t>856451</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>896579</t>
+          <t>894780</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1509630</t>
+          <t>1509517</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1562621</t>
+          <t>1563466</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,33%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46139</t>
+          <t>45789</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74484</t>
+          <t>73600</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55871</t>
+          <t>56350</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89956</t>
+          <t>89656</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110183</t>
+          <t>109421</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>157090</t>
+          <t>155461</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17242</t>
+          <t>17833</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39232</t>
+          <t>40970</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24674</t>
+          <t>23210</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49645</t>
+          <t>46657</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>48757</t>
+          <t>48341</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>79163</t>
+          <t>79155</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1791143</t>
+          <t>1795207</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1856280</t>
+          <t>1854608</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1721575</t>
+          <t>1722388</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1780239</t>
+          <t>1778696</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3538237</t>
+          <t>3531889</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3623173</t>
+          <t>3617226</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,63%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>150590</t>
+          <t>150508</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>207856</t>
+          <t>204564</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>141615</t>
+          <t>140041</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>192991</t>
+          <t>189977</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>305527</t>
+          <t>307516</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>379914</t>
+          <t>381145</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43764</t>
+          <t>45520</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75795</t>
+          <t>77905</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43252</t>
+          <t>44197</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73731</t>
+          <t>74270</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96396</t>
+          <t>96821</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>139185</t>
+          <t>139789</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>482914</t>
+          <t>483666</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>508366</t>
+          <t>509052</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,82 +5770,82 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>89,86%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>94,58%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>493873</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>478967</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>506963</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>90,95%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>88,21%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>93,36%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>990820</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>970122</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>1008057</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>91,64%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>89,72%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>94,45%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>493873</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>479988</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>507270</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>90,95%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>88,39%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>93,42%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>931</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>990820</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>970401</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>1009082</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>91,64%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>89,75%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20880</t>
+          <t>20822</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44348</t>
+          <t>42784</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23059</t>
+          <t>23382</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46540</t>
+          <t>47445</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51403</t>
+          <t>50155</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84106</t>
+          <t>82811</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19246</t>
+          <t>19495</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8415</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24093</t>
+          <t>24350</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16333</t>
+          <t>16145</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37561</t>
+          <t>36527</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2948091</t>
+          <t>2945698</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3019971</t>
+          <t>3020157</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3080789</t>
+          <t>3083617</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3159107</t>
+          <t>3154611</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6053863</t>
+          <t>6054236</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6159257</t>
+          <t>6158414</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,94%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>238025</t>
+          <t>237164</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>302151</t>
+          <t>303355</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>239601</t>
+          <t>241529</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>305070</t>
+          <t>305006</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>494730</t>
+          <t>495009</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>589352</t>
+          <t>585271</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>77797</t>
+          <t>75459</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>118176</t>
+          <t>115604</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>89454</t>
+          <t>87967</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>130077</t>
+          <t>131878</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>174578</t>
+          <t>176601</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>230972</t>
+          <t>234687</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2023</t>
+          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2023 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>471104</t>
+          <t>470749</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>490565</t>
+          <t>490204</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>700979</t>
+          <t>700681</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>720273</t>
+          <t>719634</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1179741</t>
+          <t>1178755</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1206557</t>
+          <t>1206290</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22684</t>
+          <t>23634</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21191</t>
+          <t>20761</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37739</t>
+          <t>37602</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33099</t>
+          <t>32492</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54506</t>
+          <t>54609</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23522</t>
+          <t>23480</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6188</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15283</t>
+          <t>15578</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16613</t>
+          <t>16998</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33933</t>
+          <t>34668</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2160852</t>
+          <t>2158775</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2223172</t>
+          <t>2219225</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2111731</t>
+          <t>2113392</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2163340</t>
+          <t>2164764</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4286215</t>
+          <t>4281295</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4363972</t>
+          <t>4359527</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51142</t>
+          <t>52320</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>99702</t>
+          <t>102362</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52196</t>
+          <t>52123</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93019</t>
+          <t>92384</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>117272</t>
+          <t>122106</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>179716</t>
+          <t>187907</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11772</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39593</t>
+          <t>38015</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15134</t>
+          <t>16126</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36738</t>
+          <t>37756</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33548</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70936</t>
+          <t>68618</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>597729</t>
+          <t>596995</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>621358</t>
+          <t>621694</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>620686</t>
+          <t>619086</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>638170</t>
+          <t>637010</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1224839</t>
+          <t>1224489</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1254873</t>
+          <t>1254171</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15147</t>
+          <t>16028</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35527</t>
+          <t>36581</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15210</t>
+          <t>16091</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31552</t>
+          <t>32551</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34126</t>
+          <t>36004</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60696</t>
+          <t>64246</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5452</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19653</t>
+          <t>20613</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1741</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8915</t>
+          <t>8822</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8868</t>
+          <t>8572</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25253</t>
+          <t>24792</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3250483</t>
+          <t>3250864</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3318195</t>
+          <t>3320330</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3449604</t>
+          <t>3447713</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3507139</t>
+          <t>3504682</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,47 +8316,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>94,74%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>96,3%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>8270</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>6757802</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>6716319</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>6806295</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>95,37%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>94,79%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>96,37%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>8270</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>6757802</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>6713646</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>6807121</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>95,37%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>94,75%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90802</t>
+          <t>88846</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>143907</t>
+          <t>144378</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99567</t>
+          <t>100906</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>148119</t>
+          <t>148964</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>201955</t>
+          <t>204262</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>281255</t>
+          <t>274632</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32890</t>
+          <t>31747</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>67795</t>
+          <t>65094</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28006</t>
+          <t>28944</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>52313</t>
+          <t>55169</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>69470</t>
+          <t>67721</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>109440</t>
+          <t>109872</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05A04-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P05A04-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>879062</t>
+          <t>878133</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>921239</t>
+          <t>918661</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1135670</t>
+          <t>1134101</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1181643</t>
+          <t>1178973</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2025232</t>
+          <t>2028046</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2087774</t>
+          <t>2087958</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,79%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85537</t>
+          <t>87731</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>124797</t>
+          <t>126646</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>95240</t>
+          <t>96902</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136765</t>
+          <t>136795</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>193378</t>
+          <t>193292</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>248770</t>
+          <t>249607</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12894</t>
+          <t>12464</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30192</t>
+          <t>29487</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17348</t>
+          <t>16460</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36872</t>
+          <t>37640</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34976</t>
+          <t>34544</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61447</t>
+          <t>61389</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1484356</t>
+          <t>1482493</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1531899</t>
+          <t>1534094</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1380769</t>
+          <t>1379456</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1430079</t>
+          <t>1430905</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2883994</t>
+          <t>2882957</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2952282</t>
+          <t>2950189</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,79%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>121091</t>
+          <t>121728</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>166317</t>
+          <t>166286</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>104872</t>
+          <t>107052</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>149431</t>
+          <t>152241</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>237976</t>
+          <t>239102</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>302445</t>
+          <t>302428</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14087</t>
+          <t>13285</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31942</t>
+          <t>32374</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29109</t>
+          <t>29228</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54138</t>
+          <t>54595</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46251</t>
+          <t>47017</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79135</t>
+          <t>79541</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>466388</t>
+          <t>468344</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>498958</t>
+          <t>498954</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>404444</t>
+          <t>405341</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>432129</t>
+          <t>433682</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>882456</t>
+          <t>883444</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>924273</t>
+          <t>923600</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,96%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30311</t>
+          <t>31092</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56665</t>
+          <t>57730</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32891</t>
+          <t>31304</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59060</t>
+          <t>58416</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70561</t>
+          <t>70550</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>108298</t>
+          <t>106387</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,48%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>9615</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27175</t>
+          <t>26990</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13095</t>
+          <t>13419</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13897</t>
+          <t>14224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35131</t>
+          <t>34481</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2859621</t>
+          <t>2860945</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2929945</t>
+          <t>2930565</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2949403</t>
+          <t>2948078</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3023021</t>
+          <t>3020706</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5833430</t>
+          <t>5832637</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5931113</t>
+          <t>5933824</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,04%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>256541</t>
+          <t>259641</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>326232</t>
+          <t>322953</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>256036</t>
+          <t>255920</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>321217</t>
+          <t>321049</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>533690</t>
+          <t>529305</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>626340</t>
+          <t>622290</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44741</t>
+          <t>43623</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>77251</t>
+          <t>73968</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56876</t>
+          <t>58299</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>90920</t>
+          <t>93521</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>109209</t>
+          <t>108198</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>154712</t>
+          <t>154413</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>884453</t>
+          <t>884700</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>918087</t>
+          <t>918161</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1196727</t>
+          <t>1197791</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1238231</t>
+          <t>1241054</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2093913</t>
+          <t>2096064</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2148107</t>
+          <t>2148758</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35562</t>
+          <t>34321</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65914</t>
+          <t>64010</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72781</t>
+          <t>73410</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>111719</t>
+          <t>112931</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117090</t>
+          <t>115772</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>163840</t>
+          <t>164609</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11063</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29519</t>
+          <t>28209</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10850</t>
+          <t>11381</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28442</t>
+          <t>29808</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26992</t>
+          <t>25980</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>50811</t>
+          <t>49673</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1729175</t>
+          <t>1730038</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1783372</t>
+          <t>1784386</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1556821</t>
+          <t>1560305</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1607686</t>
+          <t>1607086</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3303961</t>
+          <t>3301846</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3377846</t>
+          <t>3375749</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,62%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>127661</t>
+          <t>126100</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>177471</t>
+          <t>175061</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>102660</t>
+          <t>101970</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>146800</t>
+          <t>143247</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>241605</t>
+          <t>240006</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>308142</t>
+          <t>308084</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27214</t>
+          <t>26071</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55988</t>
+          <t>54368</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20828</t>
+          <t>21533</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44277</t>
+          <t>44689</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,47 +3520,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>70890</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>54277</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>93995</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>2,55%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>70890</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>54601</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>91049</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>418978</t>
+          <t>418146</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>446205</t>
+          <t>446141</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>397394</t>
+          <t>397096</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>423504</t>
+          <t>422267</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>825386</t>
+          <t>825858</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>864064</t>
+          <t>862073</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,79%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21612</t>
+          <t>21687</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45650</t>
+          <t>45608</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19485</t>
+          <t>19122</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41981</t>
+          <t>41399</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45193</t>
+          <t>45612</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>78946</t>
+          <t>78072</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21220</t>
+          <t>21040</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>5570</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20261</t>
+          <t>19996</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14325</t>
+          <t>14463</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34795</t>
+          <t>34440</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3058262</t>
+          <t>3060382</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3127821</t>
+          <t>3133141</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3179207</t>
+          <t>3179927</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3249614</t>
+          <t>3249580</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6260801</t>
+          <t>6262853</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6357437</t>
+          <t>6362049</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,04%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>200662</t>
+          <t>192712</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>262825</t>
+          <t>259123</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>213612</t>
+          <t>213297</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>274691</t>
+          <t>274870</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>429685</t>
+          <t>426526</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>515539</t>
+          <t>519189</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54454</t>
+          <t>54043</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>90366</t>
+          <t>91677</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>46048</t>
+          <t>45291</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>78521</t>
+          <t>78673</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>108844</t>
+          <t>109123</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>155219</t>
+          <t>155460</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>641550</t>
+          <t>640928</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>676515</t>
+          <t>677163</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>856451</t>
+          <t>854749</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>894780</t>
+          <t>894848</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1509517</t>
+          <t>1512308</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1563466</t>
+          <t>1566097</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,48%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45789</t>
+          <t>45850</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73600</t>
+          <t>76060</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56350</t>
+          <t>55412</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89656</t>
+          <t>89184</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109421</t>
+          <t>107040</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>155461</t>
+          <t>153475</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17833</t>
+          <t>17356</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40970</t>
+          <t>38573</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23210</t>
+          <t>24969</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46657</t>
+          <t>48948</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>48341</t>
+          <t>47616</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>79155</t>
+          <t>80793</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1795207</t>
+          <t>1795691</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1854608</t>
+          <t>1856501</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1722388</t>
+          <t>1719713</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1778696</t>
+          <t>1775058</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3531889</t>
+          <t>3532100</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3617226</t>
+          <t>3614537</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,57%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>150508</t>
+          <t>151490</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>204564</t>
+          <t>206244</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>140041</t>
+          <t>141303</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>189977</t>
+          <t>192713</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>307516</t>
+          <t>310390</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>381145</t>
+          <t>384877</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45520</t>
+          <t>43541</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77905</t>
+          <t>76348</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44197</t>
+          <t>43831</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74270</t>
+          <t>72296</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96821</t>
+          <t>94541</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>139789</t>
+          <t>139243</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>483666</t>
+          <t>480846</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>509052</t>
+          <t>508856</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>478967</t>
+          <t>479828</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>506963</t>
+          <t>506691</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>970122</t>
+          <t>970966</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1008057</t>
+          <t>1007475</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,18%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20822</t>
+          <t>20957</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42784</t>
+          <t>45305</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23382</t>
+          <t>23877</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47445</t>
+          <t>46633</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50155</t>
+          <t>48936</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82811</t>
+          <t>80951</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19495</t>
+          <t>19469</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8378</t>
+          <t>7922</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24350</t>
+          <t>24840</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16145</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36527</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2945698</t>
+          <t>2942990</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3020157</t>
+          <t>3019356</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3083617</t>
+          <t>3085052</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3154611</t>
+          <t>3158404</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6054236</t>
+          <t>6049939</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6158414</t>
+          <t>6157165</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,92%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>237164</t>
+          <t>235025</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>303355</t>
+          <t>301645</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>241529</t>
+          <t>239182</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>305006</t>
+          <t>300631</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>495009</t>
+          <t>494374</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>585271</t>
+          <t>584007</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>75459</t>
+          <t>76644</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>115604</t>
+          <t>118723</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>87967</t>
+          <t>87541</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>131878</t>
+          <t>127874</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>176601</t>
+          <t>176334</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>234687</t>
+          <t>233730</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -6893,32 +6893,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>482175</t>
+          <t>540045</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>470749</t>
+          <t>526594</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>490204</t>
+          <t>551084</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,32 +6928,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>711411</t>
+          <t>774303</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>700681</t>
+          <t>764525</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>719634</t>
+          <t>783587</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1193588</t>
+          <t>1314349</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1178755</t>
+          <t>1297113</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1206290</t>
+          <t>1329808</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7006,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14864</t>
+          <t>19554</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>11914</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23634</t>
+          <t>29949</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27990</t>
+          <t>30203</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20761</t>
+          <t>22311</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37602</t>
+          <t>39036</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>42854</t>
+          <t>49757</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32492</t>
+          <t>38217</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54609</t>
+          <t>64892</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14456</t>
+          <t>15470</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8510</t>
+          <t>8819</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23480</t>
+          <t>25183</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9877</t>
+          <t>10612</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6199</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15578</t>
+          <t>16214</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>24333</t>
+          <t>26082</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16998</t>
+          <t>17979</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34668</t>
+          <t>37719</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>511496</t>
+          <t>575069</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>511496</t>
+          <t>575069</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>511496</t>
+          <t>575069</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>749278</t>
+          <t>815118</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>749278</t>
+          <t>815118</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>749278</t>
+          <t>815118</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1260775</t>
+          <t>1390188</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1260775</t>
+          <t>1390188</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1260775</t>
+          <t>1390188</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7349,32 +7349,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2188365</t>
+          <t>2120845</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2158775</t>
+          <t>2094294</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2219225</t>
+          <t>2140623</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,32 +7384,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2134930</t>
+          <t>2055135</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2113392</t>
+          <t>2030512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2164764</t>
+          <t>2072729</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4323295</t>
+          <t>4175980</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4281295</t>
+          <t>4142551</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4359527</t>
+          <t>4204036</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>78207</t>
+          <t>85958</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52320</t>
+          <t>68780</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>102362</t>
+          <t>109856</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7497,67 +7497,67 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>73449</t>
+          <t>83220</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52123</t>
+          <t>67459</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>92384</t>
+          <t>104299</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>169178</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>144674</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>200003</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>3,29%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>151656</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>122106</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>187907</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22750</t>
+          <t>22829</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>13800</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38015</t>
+          <t>40837</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24912</t>
+          <t>25744</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16126</t>
+          <t>17140</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37756</t>
+          <t>37274</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>47662</t>
+          <t>48573</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>36701</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68618</t>
+          <t>65880</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2289322</t>
+          <t>2229632</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2289322</t>
+          <t>2229632</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2289322</t>
+          <t>2229632</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7723,17 +7723,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2233291</t>
+          <t>2164099</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2233291</t>
+          <t>2164099</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2233291</t>
+          <t>2164099</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4522613</t>
+          <t>4393731</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4522613</t>
+          <t>4393731</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4522613</t>
+          <t>4393731</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7805,32 +7805,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>611204</t>
+          <t>672632</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>596995</t>
+          <t>658690</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>621694</t>
+          <t>685179</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7840,32 +7840,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>629715</t>
+          <t>699300</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>619086</t>
+          <t>688988</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>637010</t>
+          <t>707565</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1240919</t>
+          <t>1371932</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1224489</t>
+          <t>1354264</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1254171</t>
+          <t>1387649</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -7918,32 +7918,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24073</t>
+          <t>25848</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16028</t>
+          <t>16685</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36581</t>
+          <t>36414</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7953,32 +7953,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22800</t>
+          <t>24703</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16091</t>
+          <t>17112</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32551</t>
+          <t>35090</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>46874</t>
+          <t>50551</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36004</t>
+          <t>37674</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64246</t>
+          <t>65868</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -8031,32 +8031,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10436</t>
+          <t>12146</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20613</t>
+          <t>23211</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8066,32 +8066,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>2559</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8822</t>
+          <t>10174</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>14624</t>
+          <t>17542</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8572</t>
+          <t>10642</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24792</t>
+          <t>27993</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -8144,17 +8144,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>645713</t>
+          <t>710626</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>645713</t>
+          <t>710626</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>645713</t>
+          <t>710626</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>656704</t>
+          <t>729398</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>656704</t>
+          <t>729398</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>656704</t>
+          <t>729398</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1302417</t>
+          <t>1440024</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1302417</t>
+          <t>1440024</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1302417</t>
+          <t>1440024</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3281746</t>
+          <t>3333522</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3250864</t>
+          <t>3302605</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3320330</t>
+          <t>3361172</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3476056</t>
+          <t>3528739</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3447713</t>
+          <t>3503752</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3504682</t>
+          <t>3550910</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6757802</t>
+          <t>6862261</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6716319</t>
+          <t>6820501</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6806295</t>
+          <t>6894912</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>117144</t>
+          <t>131360</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88846</t>
+          <t>108511</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>144378</t>
+          <t>158108</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>124239</t>
+          <t>138125</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>100906</t>
+          <t>119205</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>148964</t>
+          <t>161191</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>241383</t>
+          <t>269485</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>204262</t>
+          <t>239227</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>274632</t>
+          <t>301411</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>47642</t>
+          <t>50445</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31747</t>
+          <t>36502</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>65094</t>
+          <t>67110</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>38978</t>
+          <t>41752</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28944</t>
+          <t>31807</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55169</t>
+          <t>56116</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>86620</t>
+          <t>92197</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>67721</t>
+          <t>73025</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>109872</t>
+          <t>114921</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3446532</t>
+          <t>3515327</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3446532</t>
+          <t>3515327</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3446532</t>
+          <t>3515327</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3639273</t>
+          <t>3708616</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3639273</t>
+          <t>3708616</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3639273</t>
+          <t>3708616</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7085805</t>
+          <t>7223943</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7085805</t>
+          <t>7223943</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7085805</t>
+          <t>7223943</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
